--- a/examples/results/Tryptophan_design_results_ecFactory_level_3_result.xlsx
+++ b/examples/results/Tryptophan_design_results_ecFactory_level_3_result.xlsx
@@ -429,6 +429,11 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0</t>
+        </is>
+      </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
           <t>gene_name</t>
@@ -466,7 +471,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>b1264</t>
         </is>
@@ -487,14 +492,14 @@
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.25</v>
+        <v>-1</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.25</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>b1262</t>
         </is>
@@ -515,14 +520,14 @@
         <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.25</v>
+        <v>-1</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.25</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>b1263</t>
         </is>
@@ -543,14 +548,14 @@
         <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.25</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.25</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>b1693</t>
         </is>
@@ -571,14 +576,14 @@
         <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.25</v>
+        <v>1.248531009433552e-14</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.25</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>b3389</t>
         </is>
@@ -599,14 +604,14 @@
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.25</v>
+        <v>9.908976265345648e-16</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.25</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>b2329</t>
         </is>
@@ -627,14 +632,14 @@
         <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.25</v>
+        <v>-1.98179525306913e-16</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.25</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>b3870</t>
         </is>
@@ -655,14 +660,14 @@
         <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>-4.753335914486308e-13</v>
+        <v>1.330379153385307e-12</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.25</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>b0767</t>
         </is>
@@ -683,38 +688,38 @@
         <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.2500000000000001</v>
+        <v>8.820970671410697e-13</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.25</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>b2029</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>0.1824571256088911</v>
+        <v>1000</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>OE</t>
         </is>
       </c>
       <c r="E10" t="n">
         <v>2</v>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.2438761579269342</v>
+        <v>1.940177552754678e-13</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.25</v>
+        <v>-1</v>
       </c>
     </row>
   </sheetData>
